--- a/input/reg_wages.xlsx
+++ b/input/reg_wages.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="52">
   <si>
     <t>Description:</t>
   </si>
@@ -179,7 +179,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="9">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -220,6 +220,46 @@
       <name val="Calibri"/>
       <b/>
     </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -229,7 +269,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -265,11 +305,39 @@
       <bottom style="none"/>
       <diagonal style="none"/>
     </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
@@ -284,6 +352,22 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -308,7 +392,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="5" t="s">
         <v>2</v>
       </c>
       <c r="B2" t="s">
@@ -321,10 +405,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="7" t="s">
         <v>0</v>
       </c>
     </row>
@@ -361,7 +445,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="8" t="s">
         <v>14</v>
       </c>
       <c r="B11" t="s">
